--- a/exports/prints/relatorio_financeiro.xlsx
+++ b/exports/prints/relatorio_financeiro.xlsx
@@ -588,7 +588,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ENERGÉTICA NORTE  ·  Resumo Executivo  ·  Jan/2023 – Dez/2024</t>
+          <t>ENERGÉTICA MIRAMAR  ·  Resumo Executivo  ·  Jan/2023 – Dez/2024</t>
         </is>
       </c>
     </row>
